--- a/tabela de saída.xlsx
+++ b/tabela de saída.xlsx
@@ -25968,7 +25968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26009,25 +26009,30 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>CPLEX Status</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Obj médio do ILS</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ILS Tempo até Melhor</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Melhor Obj do ILS</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Gap Melhor obj ILS vs CPLEX (%)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Gap ILS vs CPLEX (%)(Média do obj encontrado)</t>
         </is>
@@ -26057,19 +26062,24 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>160572.07</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>11.49</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>150695.5</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>9.18</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>16.32</v>
       </c>
     </row>
@@ -26097,19 +26107,24 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>172612.46</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>17.53</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>165689.6</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6.29</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>10.67</v>
       </c>
     </row>
@@ -26137,19 +26152,24 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>220263.67</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>17.13</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>205889.1</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5.73</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>13.07</v>
       </c>
     </row>
@@ -26177,19 +26197,24 @@
       <c r="G5" t="n">
         <v>1.11</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>268761.24</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>16.04</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>257030.8</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>8.91</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>13.86</v>
       </c>
     </row>
@@ -26217,19 +26242,24 @@
       <c r="G6" t="n">
         <v>22.95</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>333865.82</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>19.78</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>317455.4</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>7.79</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>13.36</v>
       </c>
     </row>
@@ -26257,19 +26287,24 @@
       <c r="G7" t="n">
         <v>40.15</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>403409.92</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>18.83</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>382679.2</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3.87</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>9.470000000000001</v>
       </c>
     </row>
@@ -26297,19 +26332,24 @@
       <c r="G8" t="n">
         <v>47.84</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>474397.34</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>18.85</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>453862.7</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>0.45</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>5.02</v>
       </c>
     </row>
@@ -26337,19 +26377,24 @@
       <c r="G9" t="n">
         <v>55.63</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>568553.98</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>18.74</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>551315.8</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>0.17</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>3.29</v>
       </c>
     </row>
@@ -26377,19 +26422,24 @@
       <c r="G10" t="n">
         <v>62.67</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>680512.12</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>21.02</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>660218.1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>-2.97</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -26417,19 +26467,24 @@
       <c r="G11" t="n">
         <v>68.75</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>847544.42</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>21.2</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>829661.1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>-3.66</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>-1.59</v>
       </c>
     </row>
@@ -26457,19 +26512,24 @@
       <c r="G12" t="n">
         <v>77.01000000000001</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>1180123.17</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>21.52</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>1165622.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>-8.119999999999999</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>-6.98</v>
       </c>
     </row>
@@ -26497,19 +26557,24 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>159536.16</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>15.11</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>155360.3</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>12.33</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>15.36</v>
       </c>
     </row>
@@ -26537,19 +26602,24 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>169505.47</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>17.34</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>166796.1</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>8.93</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>10.64</v>
       </c>
     </row>
@@ -26577,19 +26647,24 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>222112.39</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>16.89</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>206513.2</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>5.71</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>13.69</v>
       </c>
     </row>
@@ -26617,19 +26692,24 @@
       <c r="G16" t="n">
         <v>5.32</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>266249.67</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>16.36</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>254161.5</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>8.07</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>13.23</v>
       </c>
     </row>
@@ -26657,19 +26737,24 @@
       <c r="G17" t="n">
         <v>24.97</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>327298.87</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>16.91</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>306891.6</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>5.41</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>12.47</v>
       </c>
     </row>
@@ -26697,19 +26782,24 @@
       <c r="G18" t="n">
         <v>39.64</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>394002.53</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>17.79</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>375800</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>4.25</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>9.289999999999999</v>
       </c>
     </row>
@@ -26737,19 +26827,24 @@
       <c r="G19" t="n">
         <v>50.3</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>468314.42</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>18.76</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>446980.4</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1.94</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>6.8</v>
       </c>
     </row>
@@ -26777,19 +26872,24 @@
       <c r="G20" t="n">
         <v>56.51</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>545972.89</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>19.39</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>521280.9</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>-1.8</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>2.89</v>
       </c>
     </row>
@@ -26817,19 +26917,24 @@
       <c r="G21" t="n">
         <v>61.56</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>644078.6</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>22.01</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>622684.6</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>-4.37</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>-1.08</v>
       </c>
     </row>
@@ -26857,19 +26962,24 @@
       <c r="G22" t="n">
         <v>66.69</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>796396.03</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>21.34</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>780083.6</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>-3.46</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>-1.45</v>
       </c>
     </row>
@@ -26897,19 +27007,24 @@
       <c r="G23" t="n">
         <v>77.34</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>1180453.8</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>21.17</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>1168212.9</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>-8.369999999999999</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>-7.41</v>
       </c>
     </row>
@@ -26937,19 +27052,24 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>161635.21</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>14.3</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>157778.3</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>15</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>17.86</v>
       </c>
     </row>
@@ -26977,19 +27097,24 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>171019.17</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>18.63</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>165221.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>8.19</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>11.8</v>
       </c>
     </row>
@@ -27017,19 +27142,24 @@
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>217005.62</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>16.33</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>204334.6</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>7.51</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>14.17</v>
       </c>
     </row>
@@ -27057,19 +27187,24 @@
       <c r="G27" t="n">
         <v>5.21</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>265347.54</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>17.09</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>253496.1</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>14.41</v>
       </c>
     </row>
@@ -27097,19 +27232,24 @@
       <c r="G28" t="n">
         <v>26.38</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>325924.78</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>17.45</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>307650.3</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>4.98</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>11.18</v>
       </c>
     </row>
@@ -27137,19 +27277,24 @@
       <c r="G29" t="n">
         <v>39.44</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>390139.84</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>18.88</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>370298.8</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4.02</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>9.57</v>
       </c>
     </row>
@@ -27177,19 +27322,24 @@
       <c r="G30" t="n">
         <v>48.29</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>465600.22</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>19.18</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>445810.5</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1.91</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>6.44</v>
       </c>
     </row>
@@ -27217,19 +27367,24 @@
       <c r="G31" t="n">
         <v>55.6</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
         <v>542726.97</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>19.21</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>521584.6</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>0.32</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>4.39</v>
       </c>
     </row>
@@ -27257,19 +27412,24 @@
       <c r="G32" t="n">
         <v>61.35</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
         <v>642277.41</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>21.09</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>624605.9</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>-3.41</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>-0.67</v>
       </c>
     </row>
@@ -27297,19 +27457,24 @@
       <c r="G33" t="n">
         <v>66.78</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>782719.9300000001</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>22.89</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>765467.3</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>-3.26</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>-1.06</v>
       </c>
     </row>
@@ -27337,19 +27502,24 @@
       <c r="G34" t="n">
         <v>77.41</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Feasible</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>1186096.66</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>20.49</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>1172957.5</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>-8.23</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>-7.2</v>
       </c>
     </row>
